--- a/output/yearly_benthic_cover_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_23_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.85491984205491</v>
+        <v>45.35664546934203</v>
       </c>
       <c r="M2" t="n">
-        <v>100.8702533126647</v>
+        <v>100.0052011101597</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02986595261272</v>
+        <v>87.92409245495716</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89435183341661</v>
+        <v>45.86287154786454</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228763213127631</v>
+        <v>2.228515523796102</v>
       </c>
       <c r="E3" t="n">
-        <v>5.687014708444892</v>
+        <v>5.663186524518391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429210710425438</v>
+        <v>0.742838507932034</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96115228099143</v>
+        <v>33.95134328137127</v>
       </c>
       <c r="H3" t="n">
-        <v>34.174369267957</v>
+        <v>34.17057136487356</v>
       </c>
       <c r="I3" t="n">
-        <v>6.592388717033309</v>
+        <v>6.524896577890607</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643256694015898</v>
+        <v>4.642740674575212</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97013404738729</v>
+        <v>12.07590754504284</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89888463148009</v>
+        <v>48.82698797460576</v>
       </c>
       <c r="M3" t="n">
-        <v>106.763370512284</v>
+        <v>106.7657670675131</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.21770965283589</v>
+        <v>86.92797360413033</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72330451786206</v>
+        <v>42.4960006226091</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190137241586736</v>
+        <v>2.18000868259059</v>
       </c>
       <c r="E4" t="n">
-        <v>6.505990901639759</v>
+        <v>6.448048244805201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444841866744808</v>
+        <v>0.7443905820099526</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37258257839807</v>
+        <v>33.21234353033611</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24627258702611</v>
+        <v>34.24196677245781</v>
       </c>
       <c r="I4" t="n">
-        <v>5.505215990795241</v>
+        <v>5.448774654368455</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653026166715504</v>
+        <v>4.652441137562203</v>
       </c>
       <c r="K4" t="n">
-        <v>12.78229034716413</v>
+        <v>13.07202639586967</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31128322616733</v>
+        <v>44.25072585435761</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8168780911935</v>
+        <v>99.81875287283637</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.21992069646512</v>
+        <v>85.68194653656803</v>
       </c>
       <c r="C5" t="n">
-        <v>42.58001928398315</v>
+        <v>42.09553822973074</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141990505230732</v>
+        <v>2.118829840852304</v>
       </c>
       <c r="E5" t="n">
-        <v>7.128938770029899</v>
+        <v>7.025206390293418</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458069760075922</v>
+        <v>0.7457078548568493</v>
       </c>
       <c r="G5" t="n">
-        <v>32.6389386293289</v>
+        <v>32.28028636706581</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30712089634923</v>
+        <v>34.30256132341506</v>
       </c>
       <c r="I5" t="n">
-        <v>4.595831319471303</v>
+        <v>4.548680667229283</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661293600047451</v>
+        <v>4.660674092855308</v>
       </c>
       <c r="K5" t="n">
-        <v>13.78007930353491</v>
+        <v>14.31805346343197</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48697874607098</v>
+        <v>43.43505345532706</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84707733358903</v>
+        <v>99.84864514848977</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.00029450782866</v>
+        <v>84.26192104348607</v>
       </c>
       <c r="C6" t="n">
-        <v>42.07435859744282</v>
+        <v>41.38176616376828</v>
       </c>
       <c r="D6" t="n">
-        <v>2.082784210053595</v>
+        <v>2.049269284047639</v>
       </c>
       <c r="E6" t="n">
-        <v>7.571159344447734</v>
+        <v>7.427280906517688</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469287886960658</v>
+        <v>0.7468277362548308</v>
       </c>
       <c r="G6" t="n">
-        <v>31.73677280271225</v>
+        <v>31.22053411598183</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35872428001901</v>
+        <v>34.35407586772221</v>
       </c>
       <c r="I6" t="n">
-        <v>3.835620152549585</v>
+        <v>3.796259781369166</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668304929350411</v>
+        <v>4.667673351592692</v>
       </c>
       <c r="K6" t="n">
-        <v>14.99970549217135</v>
+        <v>15.73807895651393</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79827392928943</v>
+        <v>42.75380263896144</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87233801890359</v>
+        <v>99.87364775924365</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.64266293649284</v>
+        <v>82.47692495019345</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31273859576127</v>
+        <v>40.18617425247731</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017037404961262</v>
+        <v>1.961895627088144</v>
       </c>
       <c r="E7" t="n">
-        <v>7.865566649716365</v>
+        <v>7.638540987921917</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478814488498603</v>
+        <v>0.7477838224072364</v>
       </c>
       <c r="G7" t="n">
-        <v>30.73494486218553</v>
+        <v>29.88940000921668</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40254664709356</v>
+        <v>34.39805583073286</v>
       </c>
       <c r="I7" t="n">
-        <v>3.200426868374652</v>
+        <v>3.16759978278138</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674259055311627</v>
+        <v>4.673648890045228</v>
       </c>
       <c r="K7" t="n">
-        <v>16.35733706350716</v>
+        <v>17.52307504980654</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22337933649408</v>
+        <v>42.18529903712254</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8934549957625</v>
+        <v>99.89454833940638</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.61528119317134</v>
+        <v>87.30608034383751</v>
       </c>
       <c r="C8" t="n">
-        <v>43.65789888558338</v>
+        <v>42.44000293112306</v>
       </c>
       <c r="D8" t="n">
-        <v>2.02136447801593</v>
+        <v>1.966104898464121</v>
       </c>
       <c r="E8" t="n">
-        <v>9.730869603486065</v>
+        <v>9.438528516364769</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494858502642536</v>
+        <v>0.7493882018633187</v>
       </c>
       <c r="G8" t="n">
-        <v>31.24983657138364</v>
+        <v>30.37703686655496</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47634911215565</v>
+        <v>34.47185728571264</v>
       </c>
       <c r="I8" t="n">
-        <v>5.703089013714203</v>
+        <v>5.619488313231959</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684286564151585</v>
+        <v>4.683676261645742</v>
       </c>
       <c r="K8" t="n">
-        <v>11.38471880682866</v>
+        <v>12.69391965616249</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76768628806596</v>
+        <v>44.67916216458747</v>
       </c>
       <c r="M8" t="n">
-        <v>99.810303980478</v>
+        <v>99.81308475187302</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.94876014573569</v>
+        <v>85.16722602058296</v>
       </c>
       <c r="C9" t="n">
-        <v>42.87713115206343</v>
+        <v>41.17268864794151</v>
       </c>
       <c r="D9" t="n">
-        <v>1.94657425993626</v>
+        <v>1.868882948089856</v>
       </c>
       <c r="E9" t="n">
-        <v>10.16437023170414</v>
+        <v>9.753720187969277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508538930892605</v>
+        <v>0.7507642237396074</v>
       </c>
       <c r="G9" t="n">
-        <v>30.09359675538475</v>
+        <v>28.87492231861579</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53927908210597</v>
+        <v>34.53515429202192</v>
       </c>
       <c r="I9" t="n">
-        <v>4.761249091707433</v>
+        <v>4.691505651773966</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692836831807878</v>
+        <v>4.692276398372546</v>
       </c>
       <c r="K9" t="n">
-        <v>13.05123985426432</v>
+        <v>14.83277397941703</v>
       </c>
       <c r="L9" t="n">
-        <v>43.9132098544024</v>
+        <v>43.83844047505168</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84158086073015</v>
+        <v>99.84390310241022</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.0921739861321</v>
+        <v>82.87421085839878</v>
       </c>
       <c r="C10" t="n">
-        <v>41.76009357658129</v>
+        <v>39.60687252342116</v>
       </c>
       <c r="D10" t="n">
-        <v>1.863840998880412</v>
+        <v>1.76584149011822</v>
       </c>
       <c r="E10" t="n">
-        <v>10.39467838364206</v>
+        <v>9.868569969681463</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520227457212808</v>
+        <v>0.751946658997673</v>
       </c>
       <c r="G10" t="n">
-        <v>28.81455929572256</v>
+        <v>27.28289425844812</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5930463031789</v>
+        <v>34.58954631389294</v>
       </c>
       <c r="I10" t="n">
-        <v>3.973884098228865</v>
+        <v>3.915745548524889</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700142160758005</v>
+        <v>4.699666618735456</v>
       </c>
       <c r="K10" t="n">
-        <v>14.90782601386791</v>
+        <v>17.12578914160122</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19982349033671</v>
+        <v>43.13701873353944</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86774308078591</v>
+        <v>99.86968039856183</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.98930921193697</v>
+        <v>80.55010082829401</v>
       </c>
       <c r="C11" t="n">
-        <v>40.27416499674743</v>
+        <v>37.88899589554694</v>
       </c>
       <c r="D11" t="n">
-        <v>1.770771163909388</v>
+        <v>1.662631996797035</v>
       </c>
       <c r="E11" t="n">
-        <v>10.42828951502053</v>
+        <v>9.836363017205811</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530243578397621</v>
+        <v>0.7529634220425038</v>
       </c>
       <c r="G11" t="n">
-        <v>27.37572074671189</v>
+        <v>25.68826999092036</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63912046062904</v>
+        <v>34.63631741395515</v>
       </c>
       <c r="I11" t="n">
-        <v>3.315980731327846</v>
+        <v>3.267533599607502</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706402236498513</v>
+        <v>4.706021387765649</v>
       </c>
       <c r="K11" t="n">
-        <v>17.01069078806303</v>
+        <v>19.44989917170599</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6047585457943</v>
+        <v>42.55233422306581</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88961433060476</v>
+        <v>99.89122929031873</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.7970106704215</v>
+        <v>78.02312671238785</v>
       </c>
       <c r="C12" t="n">
-        <v>38.59606012131717</v>
+        <v>35.86707842211613</v>
       </c>
       <c r="D12" t="n">
-        <v>1.674585969455908</v>
+        <v>1.551456525533562</v>
       </c>
       <c r="E12" t="n">
-        <v>10.32292157658685</v>
+        <v>9.632986070259982</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538838038853388</v>
+        <v>0.7538403695579613</v>
       </c>
       <c r="G12" t="n">
-        <v>25.88871944637821</v>
+        <v>23.97056846244885</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67865497872557</v>
+        <v>34.6766569996662</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766471121106236</v>
+        <v>2.726115975184041</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711773774283367</v>
+        <v>4.711502309737258</v>
       </c>
       <c r="K12" t="n">
-        <v>19.20298932957851</v>
+        <v>21.97687328761217</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10883997323409</v>
+        <v>42.06528346806039</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90788942412978</v>
+        <v>99.90923517778867</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.59881548459995</v>
+        <v>75.56341779677314</v>
       </c>
       <c r="C13" t="n">
-        <v>36.82614771063841</v>
+        <v>33.82776973096123</v>
       </c>
       <c r="D13" t="n">
-        <v>1.578968652068695</v>
+        <v>1.444352410546218</v>
       </c>
       <c r="E13" t="n">
-        <v>10.11810039016708</v>
+        <v>9.346984176335694</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546216008628969</v>
+        <v>0.7545965841768731</v>
       </c>
       <c r="G13" t="n">
-        <v>24.41049739674695</v>
+        <v>22.31577087150045</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71259363969324</v>
+        <v>34.71144287213615</v>
       </c>
       <c r="I13" t="n">
-        <v>2.307648799667982</v>
+        <v>2.274042230972299</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716385005393105</v>
+        <v>4.716228651105458</v>
       </c>
       <c r="K13" t="n">
-        <v>21.40118451540006</v>
+        <v>24.43658220322686</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6958213539308</v>
+        <v>41.65992262205683</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92315357996927</v>
+        <v>99.92427455624491</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.77753060675516</v>
+        <v>82.76031396388514</v>
       </c>
       <c r="C14" t="n">
-        <v>40.65372134882244</v>
+        <v>38.27059909868159</v>
       </c>
       <c r="D14" t="n">
-        <v>1.580799971566363</v>
+        <v>1.446104407962477</v>
       </c>
       <c r="E14" t="n">
-        <v>12.27361766752877</v>
+        <v>11.81641393192638</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755496826124153</v>
+        <v>0.7555119087584247</v>
       </c>
       <c r="G14" t="n">
-        <v>26.0909578846451</v>
+        <v>24.29899103221784</v>
       </c>
       <c r="H14" t="n">
-        <v>36.40500270534931</v>
+        <v>36.7096989653305</v>
       </c>
       <c r="I14" t="n">
-        <v>2.949800388265515</v>
+        <v>3.011644287949367</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721855163275956</v>
+        <v>4.721949429740155</v>
       </c>
       <c r="K14" t="n">
-        <v>15.22246939324483</v>
+        <v>17.23968603611484</v>
       </c>
       <c r="L14" t="n">
-        <v>44.02559648746404</v>
+        <v>44.38944834541758</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90178722953132</v>
+        <v>99.89973348021402</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.1376274531271</v>
+        <v>81.97577973846744</v>
       </c>
       <c r="C15" t="n">
-        <v>40.47066369460652</v>
+        <v>37.95077098432927</v>
       </c>
       <c r="D15" t="n">
-        <v>1.556992721829322</v>
+        <v>1.41734653732125</v>
       </c>
       <c r="E15" t="n">
-        <v>12.49886773843332</v>
+        <v>12.00013873436148</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562332971436068</v>
+        <v>0.7562837009116092</v>
       </c>
       <c r="G15" t="n">
-        <v>25.69802142120193</v>
+        <v>23.81577056973309</v>
       </c>
       <c r="H15" t="n">
-        <v>36.44049091460251</v>
+        <v>36.74719970791148</v>
       </c>
       <c r="I15" t="n">
-        <v>2.460563252768868</v>
+        <v>2.512267357530978</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726458107147542</v>
+        <v>4.726773130697558</v>
       </c>
       <c r="K15" t="n">
-        <v>15.8623725468729</v>
+        <v>18.02422026153255</v>
       </c>
       <c r="L15" t="n">
-        <v>43.58502485884653</v>
+        <v>43.9413519683618</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91806110032596</v>
+        <v>99.91634321422362</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.86848453187032</v>
+        <v>79.53271039392629</v>
       </c>
       <c r="C16" t="n">
-        <v>38.58271715356929</v>
+        <v>35.89539621966559</v>
       </c>
       <c r="D16" t="n">
-        <v>1.469346619625436</v>
+        <v>1.325510047600968</v>
       </c>
       <c r="E16" t="n">
-        <v>12.13731298091547</v>
+        <v>11.571826254485</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568651759733982</v>
+        <v>0.7569478774758165</v>
       </c>
       <c r="G16" t="n">
-        <v>24.25143057954786</v>
+        <v>22.27263576711696</v>
       </c>
       <c r="H16" t="n">
-        <v>36.47093915702071</v>
+        <v>36.77947149800403</v>
       </c>
       <c r="I16" t="n">
-        <v>2.052182668953698</v>
+        <v>2.095394715019679</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730407349833738</v>
+        <v>4.730924234223854</v>
       </c>
       <c r="K16" t="n">
-        <v>18.13151546812968</v>
+        <v>20.4672896060737</v>
       </c>
       <c r="L16" t="n">
-        <v>43.21741839905744</v>
+        <v>43.56752896988485</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93165102075642</v>
+        <v>99.93021479562414</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.41666139155936</v>
+        <v>81.39425130333387</v>
       </c>
       <c r="C17" t="n">
-        <v>39.72016712004762</v>
+        <v>37.2348611701521</v>
       </c>
       <c r="D17" t="n">
-        <v>1.470548197687429</v>
+        <v>1.32665099644726</v>
       </c>
       <c r="E17" t="n">
-        <v>12.87083397197477</v>
+        <v>12.41147309106304</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574841127029549</v>
+        <v>0.7575994295399235</v>
       </c>
       <c r="G17" t="n">
-        <v>24.65378254131364</v>
+        <v>22.77118801135515</v>
       </c>
       <c r="H17" t="n">
-        <v>36.88328378711873</v>
+        <v>37.29051067700401</v>
       </c>
       <c r="I17" t="n">
-        <v>2.046453076368368</v>
+        <v>2.10183266329998</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734275704393466</v>
+        <v>4.734996434624523</v>
       </c>
       <c r="K17" t="n">
-        <v>16.58333860844063</v>
+        <v>18.60574869666611</v>
       </c>
       <c r="L17" t="n">
-        <v>43.62833490720772</v>
+        <v>44.08938929847242</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93184063569598</v>
+        <v>99.92999916529062</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.25838723854318</v>
+        <v>79.01302224668325</v>
       </c>
       <c r="C18" t="n">
-        <v>37.87860426460266</v>
+        <v>35.17760367499085</v>
       </c>
       <c r="D18" t="n">
-        <v>1.390129928801076</v>
+        <v>1.241040514228952</v>
       </c>
       <c r="E18" t="n">
-        <v>12.45140925350081</v>
+        <v>11.90268195867263</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580143967302538</v>
+        <v>0.7581596482746996</v>
       </c>
       <c r="G18" t="n">
-        <v>23.30556796623825</v>
+        <v>21.30173418246085</v>
       </c>
       <c r="H18" t="n">
-        <v>36.90910428412803</v>
+        <v>37.31808572774463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.706571429580657</v>
+        <v>1.752822413584607</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737589979564085</v>
+        <v>4.738497801716874</v>
       </c>
       <c r="K18" t="n">
-        <v>18.74161276145682</v>
+        <v>20.98697775331675</v>
       </c>
       <c r="L18" t="n">
-        <v>43.3229370551525</v>
+        <v>43.77703433104519</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94315408121199</v>
+        <v>99.94161575935279</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.38325733497757</v>
+        <v>78.12849701758802</v>
       </c>
       <c r="C19" t="n">
-        <v>37.26701545136876</v>
+        <v>34.56058577217583</v>
       </c>
       <c r="D19" t="n">
-        <v>1.358181527310972</v>
+        <v>1.209845062441979</v>
       </c>
       <c r="E19" t="n">
-        <v>12.40241073877018</v>
+        <v>11.84740457834627</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584616875831887</v>
+        <v>0.7586330384447832</v>
       </c>
       <c r="G19" t="n">
-        <v>22.76995210263156</v>
+        <v>20.76628250779837</v>
       </c>
       <c r="H19" t="n">
-        <v>36.93088369202255</v>
+        <v>37.34138690842611</v>
       </c>
       <c r="I19" t="n">
-        <v>1.422982039264193</v>
+        <v>1.463488431850591</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740385547394927</v>
+        <v>4.741456490279897</v>
       </c>
       <c r="K19" t="n">
-        <v>19.61674266502243</v>
+        <v>21.871502982412</v>
       </c>
       <c r="L19" t="n">
-        <v>43.068837121676</v>
+        <v>43.51915873844602</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95259523806719</v>
+        <v>99.95124749303385</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.97490258925858</v>
+        <v>75.57402876104599</v>
       </c>
       <c r="C20" t="n">
-        <v>35.07828770491917</v>
+        <v>32.23095921269085</v>
       </c>
       <c r="D20" t="n">
-        <v>1.269283916851765</v>
+        <v>1.119075414198714</v>
       </c>
       <c r="E20" t="n">
-        <v>11.78836731267551</v>
+        <v>11.16191471669812</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588463643300026</v>
+        <v>0.7590413386963858</v>
       </c>
       <c r="G20" t="n">
-        <v>21.27958112386984</v>
+        <v>19.20827461317714</v>
       </c>
       <c r="H20" t="n">
-        <v>36.949614304825</v>
+        <v>37.36148423730221</v>
       </c>
       <c r="I20" t="n">
-        <v>1.186419789643945</v>
+        <v>1.220230074121007</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742789777062515</v>
+        <v>4.744008366852412</v>
       </c>
       <c r="K20" t="n">
-        <v>22.02509741074141</v>
+        <v>24.42597123895403</v>
       </c>
       <c r="L20" t="n">
-        <v>42.85708760547098</v>
+        <v>43.30241709191483</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96047272113157</v>
+        <v>99.95934754355969</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.37108866312823</v>
+        <v>81.57408784779781</v>
       </c>
       <c r="C21" t="n">
-        <v>38.36428127420754</v>
+        <v>35.96030535361938</v>
       </c>
       <c r="D21" t="n">
-        <v>1.27018215816776</v>
+        <v>1.119871312127481</v>
       </c>
       <c r="E21" t="n">
-        <v>13.57946656764659</v>
+        <v>13.17221364936082</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593833814212022</v>
+        <v>0.7595811766926918</v>
       </c>
       <c r="G21" t="n">
-        <v>22.78239863451147</v>
+        <v>20.93421455395946</v>
       </c>
       <c r="H21" t="n">
-        <v>38.46352111632303</v>
+        <v>39.10033492722349</v>
       </c>
       <c r="I21" t="n">
-        <v>1.769990671175676</v>
+        <v>1.74048987410455</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746146133882512</v>
+        <v>4.747382354329324</v>
       </c>
       <c r="K21" t="n">
-        <v>16.62891133687177</v>
+        <v>18.42591215220218</v>
       </c>
       <c r="L21" t="n">
-        <v>44.94784942299811</v>
+        <v>45.55580739752585</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94104203407741</v>
+        <v>99.94202490334742</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_23_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35664546934203</v>
+        <v>45.56869704513804</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0052011101597</v>
+        <v>99.65502237833525</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92409245495716</v>
+        <v>87.96133014537924</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86287154786454</v>
+        <v>45.87232959616418</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228515523796102</v>
+        <v>2.228604017765805</v>
       </c>
       <c r="E3" t="n">
-        <v>5.663186524518391</v>
+        <v>5.670653345358826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742838507932034</v>
+        <v>0.742868005921935</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95134328137127</v>
+        <v>33.95423214857374</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17057136487356</v>
+        <v>34.171928272409</v>
       </c>
       <c r="I3" t="n">
-        <v>6.524896577890607</v>
+        <v>6.550119318337841</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642740674575212</v>
+        <v>4.642925037012093</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07590754504284</v>
+        <v>12.03866985462076</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82698797460576</v>
+        <v>48.85387149924038</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7657670675131</v>
+        <v>106.7648709500253</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.92797360413033</v>
+        <v>86.99713652273685</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4960006226091</v>
+        <v>42.54190268919149</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18000868259059</v>
+        <v>2.181825999491021</v>
       </c>
       <c r="E4" t="n">
-        <v>6.448048244805201</v>
+        <v>6.463272728566324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443905820099526</v>
+        <v>0.7444249128493743</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21234353033611</v>
+        <v>33.24153860620792</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24196677245781</v>
+        <v>34.24354599107122</v>
       </c>
       <c r="I4" t="n">
-        <v>5.448774654368455</v>
+        <v>5.469872579242403</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652441137562203</v>
+        <v>4.652655705308589</v>
       </c>
       <c r="K4" t="n">
-        <v>13.07202639586967</v>
+        <v>13.00286347726316</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25072585435761</v>
+        <v>44.27328607470263</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81875287283637</v>
+        <v>99.81805224115729</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.68194653656803</v>
+        <v>85.74376631786089</v>
       </c>
       <c r="C5" t="n">
-        <v>42.09553822973074</v>
+        <v>42.13739656713347</v>
       </c>
       <c r="D5" t="n">
-        <v>2.118829840852304</v>
+        <v>2.120296648559983</v>
       </c>
       <c r="E5" t="n">
-        <v>7.025206390293418</v>
+        <v>7.042056071626702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457078548568493</v>
+        <v>0.7457464011387241</v>
       </c>
       <c r="G5" t="n">
-        <v>32.28028636706581</v>
+        <v>32.30409891355317</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30256132341506</v>
+        <v>34.3043344523813</v>
       </c>
       <c r="I5" t="n">
-        <v>4.548680667229283</v>
+        <v>4.566318823483968</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660674092855308</v>
+        <v>4.660915007117025</v>
       </c>
       <c r="K5" t="n">
-        <v>14.31805346343197</v>
+        <v>14.25623368213911</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43505345532706</v>
+        <v>43.45442884574847</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84864514848977</v>
+        <v>99.84805909502106</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.26192104348607</v>
+        <v>84.24309656569893</v>
       </c>
       <c r="C6" t="n">
-        <v>41.38176616376828</v>
+        <v>41.34573923042274</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049269284047639</v>
+        <v>2.046644739578239</v>
       </c>
       <c r="E6" t="n">
-        <v>7.427280906517688</v>
+        <v>7.432606244637552</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468277362548308</v>
+        <v>0.7468709413011989</v>
       </c>
       <c r="G6" t="n">
-        <v>31.22053411598183</v>
+        <v>31.18196416201538</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35407586772221</v>
+        <v>34.35606329985514</v>
       </c>
       <c r="I6" t="n">
-        <v>3.796259781369166</v>
+        <v>3.811003795178937</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667673351592692</v>
+        <v>4.667943383132492</v>
       </c>
       <c r="K6" t="n">
-        <v>15.73807895651393</v>
+        <v>15.75690343430106</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75380263896144</v>
+        <v>42.77051514573497</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87364775924365</v>
+        <v>99.87315781045876</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.47692495019345</v>
+        <v>82.49109989011953</v>
       </c>
       <c r="C7" t="n">
-        <v>40.18617425247731</v>
+        <v>40.18539549461666</v>
       </c>
       <c r="D7" t="n">
-        <v>1.961895627088144</v>
+        <v>1.960976133666044</v>
       </c>
       <c r="E7" t="n">
-        <v>7.638540987921917</v>
+        <v>7.651477882713837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477838224072364</v>
+        <v>0.7478306358740625</v>
       </c>
       <c r="G7" t="n">
-        <v>29.88940000921668</v>
+        <v>29.87674721463525</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39805583073286</v>
+        <v>34.40020925020687</v>
       </c>
       <c r="I7" t="n">
-        <v>3.16759978278138</v>
+        <v>3.17991729881056</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673648890045228</v>
+        <v>4.67394147421289</v>
       </c>
       <c r="K7" t="n">
-        <v>17.52307504980654</v>
+        <v>17.5089001098805</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18529903712254</v>
+        <v>42.19984317897008</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89454833940638</v>
+        <v>99.89413878346724</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.30608034383751</v>
+        <v>87.41416705962507</v>
       </c>
       <c r="C8" t="n">
-        <v>42.44000293112306</v>
+        <v>42.5302743830599</v>
       </c>
       <c r="D8" t="n">
-        <v>1.966104898464121</v>
+        <v>1.965189388579419</v>
       </c>
       <c r="E8" t="n">
-        <v>9.438528516364769</v>
+        <v>9.513053393176014</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493882018633187</v>
+        <v>0.7494373872500105</v>
       </c>
       <c r="G8" t="n">
-        <v>30.37703686655496</v>
+        <v>30.39397262730248</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47185728571264</v>
+        <v>34.47411981350048</v>
       </c>
       <c r="I8" t="n">
-        <v>5.619488313231959</v>
+        <v>5.634410779504111</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683676261645742</v>
+        <v>4.683983670312564</v>
       </c>
       <c r="K8" t="n">
-        <v>12.69391965616249</v>
+        <v>12.58583294037493</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67916216458747</v>
+        <v>44.69648164585081</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81308475187302</v>
+        <v>99.81258896928564</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.16722602058296</v>
+        <v>85.18952941349377</v>
       </c>
       <c r="C9" t="n">
-        <v>41.17268864794151</v>
+        <v>41.17957220288552</v>
       </c>
       <c r="D9" t="n">
-        <v>1.868882948089856</v>
+        <v>1.864205377129014</v>
       </c>
       <c r="E9" t="n">
-        <v>9.753720187969277</v>
+        <v>9.808209233462184</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507642237396074</v>
+        <v>0.7508167985110241</v>
       </c>
       <c r="G9" t="n">
-        <v>28.87492231861579</v>
+        <v>28.83213573888048</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53515429202192</v>
+        <v>34.5375727315071</v>
       </c>
       <c r="I9" t="n">
-        <v>4.691505651773966</v>
+        <v>4.703984543310071</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692276398372546</v>
+        <v>4.692604990693899</v>
       </c>
       <c r="K9" t="n">
-        <v>14.83277397941703</v>
+        <v>14.81047058650623</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83844047505168</v>
+        <v>43.85344580006647</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84390310241022</v>
+        <v>99.84348858945822</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.87421085839878</v>
+        <v>82.82403631999493</v>
       </c>
       <c r="C10" t="n">
-        <v>39.60687252342116</v>
+        <v>39.54320524105472</v>
       </c>
       <c r="D10" t="n">
-        <v>1.76584149011822</v>
+        <v>1.758108180134441</v>
       </c>
       <c r="E10" t="n">
-        <v>9.868569969681463</v>
+        <v>9.904359858586904</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751946658997673</v>
+        <v>0.7520031863178773</v>
       </c>
       <c r="G10" t="n">
-        <v>27.28289425844812</v>
+        <v>27.19121740295479</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58954631389294</v>
+        <v>34.59214657062235</v>
       </c>
       <c r="I10" t="n">
-        <v>3.915745548524889</v>
+        <v>3.926181206891842</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699666618735456</v>
+        <v>4.700019914486732</v>
       </c>
       <c r="K10" t="n">
-        <v>17.12578914160122</v>
+        <v>17.17596368000505</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13701873353944</v>
+        <v>43.15016484162607</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86968039856183</v>
+        <v>99.86933376268584</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.55010082829401</v>
+        <v>80.31011954468347</v>
       </c>
       <c r="C11" t="n">
-        <v>37.88899589554694</v>
+        <v>37.63707479808416</v>
       </c>
       <c r="D11" t="n">
-        <v>1.662631996797035</v>
+        <v>1.646590869424793</v>
       </c>
       <c r="E11" t="n">
-        <v>9.836363017205811</v>
+        <v>9.822167916199225</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529634220425038</v>
+        <v>0.7530257901532647</v>
       </c>
       <c r="G11" t="n">
-        <v>25.68826999092036</v>
+        <v>25.46647061321683</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63631741395515</v>
+        <v>34.63918634705017</v>
       </c>
       <c r="I11" t="n">
-        <v>3.267533599607502</v>
+        <v>3.276266820181272</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706021387765649</v>
+        <v>4.706411188457903</v>
       </c>
       <c r="K11" t="n">
-        <v>19.44989917170599</v>
+        <v>19.68988045531655</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55233422306581</v>
+        <v>42.56398415751895</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89122929031873</v>
+        <v>99.89093941091966</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.02312671238785</v>
+        <v>77.62767847368661</v>
       </c>
       <c r="C12" t="n">
-        <v>35.86707842211613</v>
+        <v>35.46085117635578</v>
       </c>
       <c r="D12" t="n">
-        <v>1.551456525533562</v>
+        <v>1.528798613248212</v>
       </c>
       <c r="E12" t="n">
-        <v>9.632986070259982</v>
+        <v>9.575090132776793</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538403695579613</v>
+        <v>0.7539096419764759</v>
       </c>
       <c r="G12" t="n">
-        <v>23.97056846244885</v>
+        <v>23.64467438800558</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6766569996662</v>
+        <v>34.67984353091789</v>
       </c>
       <c r="I12" t="n">
-        <v>2.726115975184041</v>
+        <v>2.733426904408707</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711502309737258</v>
+        <v>4.711935262352973</v>
       </c>
       <c r="K12" t="n">
-        <v>21.97687328761217</v>
+        <v>22.37232152631339</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06528346806039</v>
+        <v>42.07581988565913</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90923517778867</v>
+        <v>99.90899258832829</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.56341779677314</v>
+        <v>75.06346650514985</v>
       </c>
       <c r="C13" t="n">
-        <v>33.82776973096123</v>
+        <v>33.31790343308263</v>
       </c>
       <c r="D13" t="n">
-        <v>1.444352410546218</v>
+        <v>1.417417234325979</v>
       </c>
       <c r="E13" t="n">
-        <v>9.346984176335694</v>
+        <v>9.257519238716162</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545965841768731</v>
+        <v>0.7546730121141394</v>
       </c>
       <c r="G13" t="n">
-        <v>22.31577087150045</v>
+        <v>21.92202994374635</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71144287213615</v>
+        <v>34.71495855725041</v>
       </c>
       <c r="I13" t="n">
-        <v>2.274042230972299</v>
+        <v>2.28016219328345</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716228651105458</v>
+        <v>4.716706325713369</v>
       </c>
       <c r="K13" t="n">
-        <v>24.43658220322686</v>
+        <v>24.93653349485014</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65992262205683</v>
+        <v>41.66963454694478</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92427455624491</v>
+        <v>99.92407147487755</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.76031396388514</v>
+        <v>82.38317558329875</v>
       </c>
       <c r="C14" t="n">
-        <v>38.27059909868159</v>
+        <v>37.90729432942032</v>
       </c>
       <c r="D14" t="n">
-        <v>1.446104407962477</v>
+        <v>1.419089246970081</v>
       </c>
       <c r="E14" t="n">
-        <v>11.81641393192638</v>
+        <v>11.79190595381434</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555119087584247</v>
+        <v>0.7555632389209392</v>
       </c>
       <c r="G14" t="n">
-        <v>24.29899103221784</v>
+        <v>23.98545206353276</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7096989653305</v>
+        <v>36.79347146179579</v>
       </c>
       <c r="I14" t="n">
-        <v>3.011644287949367</v>
+        <v>2.915423375008976</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721949429740155</v>
+        <v>4.722270243255868</v>
       </c>
       <c r="K14" t="n">
-        <v>17.23968603611484</v>
+        <v>17.61682441670125</v>
       </c>
       <c r="L14" t="n">
-        <v>44.38944834541758</v>
+        <v>44.37881497596067</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89973348021402</v>
+        <v>99.90293372208224</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.97577973846744</v>
+        <v>81.44671590064884</v>
       </c>
       <c r="C15" t="n">
-        <v>37.95077098432927</v>
+        <v>37.42047073378391</v>
       </c>
       <c r="D15" t="n">
-        <v>1.41734653732125</v>
+        <v>1.384739054362572</v>
       </c>
       <c r="E15" t="n">
-        <v>12.00013873436148</v>
+        <v>11.91179635243578</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562837009116092</v>
+        <v>0.7563152572311193</v>
       </c>
       <c r="G15" t="n">
-        <v>23.81577056973309</v>
+        <v>23.40486497225598</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74719970791148</v>
+        <v>36.83009230676155</v>
       </c>
       <c r="I15" t="n">
-        <v>2.512267357530978</v>
+        <v>2.431937599907346</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726773130697558</v>
+        <v>4.726970357694492</v>
       </c>
       <c r="K15" t="n">
-        <v>18.02422026153255</v>
+        <v>18.55328409935116</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9413519683618</v>
+        <v>43.94526118422581</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91634321422362</v>
+        <v>99.91901601736087</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.53271039392629</v>
+        <v>78.75211297680265</v>
       </c>
       <c r="C16" t="n">
-        <v>35.89539621966559</v>
+        <v>35.10088182353746</v>
       </c>
       <c r="D16" t="n">
-        <v>1.325510047600968</v>
+        <v>1.284173605487743</v>
       </c>
       <c r="E16" t="n">
-        <v>11.571826254485</v>
+        <v>11.38477177889321</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569478774758165</v>
+        <v>0.756964583947542</v>
       </c>
       <c r="G16" t="n">
-        <v>22.27263576711696</v>
+        <v>21.70510735772609</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77947149800403</v>
+        <v>36.86171240522505</v>
       </c>
       <c r="I16" t="n">
-        <v>2.095394715019679</v>
+        <v>2.028354595850869</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730924234223854</v>
+        <v>4.731028649672134</v>
       </c>
       <c r="K16" t="n">
-        <v>20.4672896060737</v>
+        <v>21.24788702319738</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56752896988485</v>
+        <v>43.58367733104549</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93021479562414</v>
+        <v>99.93244617778034</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.39425130333387</v>
+        <v>80.57650455308153</v>
       </c>
       <c r="C17" t="n">
-        <v>37.2348611701521</v>
+        <v>36.42073124375717</v>
       </c>
       <c r="D17" t="n">
-        <v>1.32665099644726</v>
+        <v>1.285247153965925</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41147309106304</v>
+        <v>12.20808696819384</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575994295399235</v>
+        <v>0.7575973941639039</v>
       </c>
       <c r="G17" t="n">
-        <v>22.77118801135515</v>
+        <v>22.20024687292376</v>
       </c>
       <c r="H17" t="n">
-        <v>37.29051067700401</v>
+        <v>37.36952259844758</v>
       </c>
       <c r="I17" t="n">
-        <v>2.10183266329998</v>
+        <v>2.020819851862116</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734996434624523</v>
+        <v>4.734983713524397</v>
       </c>
       <c r="K17" t="n">
-        <v>18.60574869666611</v>
+        <v>19.42349544691849</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08938929847242</v>
+        <v>44.08846891298835</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92999916529062</v>
+        <v>99.932695603664</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.01302224668325</v>
+        <v>78.03259008436012</v>
       </c>
       <c r="C18" t="n">
-        <v>35.17760367499085</v>
+        <v>34.18793334439579</v>
       </c>
       <c r="D18" t="n">
-        <v>1.241040514228952</v>
+        <v>1.194505687936924</v>
       </c>
       <c r="E18" t="n">
-        <v>11.90268195867263</v>
+        <v>11.62703884413353</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581596482746996</v>
+        <v>0.7581427752558604</v>
       </c>
       <c r="G18" t="n">
-        <v>21.30173418246085</v>
+        <v>20.63285733135683</v>
       </c>
       <c r="H18" t="n">
-        <v>37.31808572774463</v>
+        <v>37.3964242631017</v>
       </c>
       <c r="I18" t="n">
-        <v>1.752822413584607</v>
+        <v>1.685228837226155</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738497801716874</v>
+        <v>4.738392345349125</v>
       </c>
       <c r="K18" t="n">
-        <v>20.98697775331675</v>
+        <v>21.96740991563987</v>
       </c>
       <c r="L18" t="n">
-        <v>43.77703433104519</v>
+        <v>43.78852285519041</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94161575935279</v>
+        <v>99.94386611522607</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.12849701758802</v>
+        <v>77.01616705119932</v>
       </c>
       <c r="C19" t="n">
-        <v>34.56058577217583</v>
+        <v>33.41360299272351</v>
       </c>
       <c r="D19" t="n">
-        <v>1.209845062441979</v>
+        <v>1.15823844679769</v>
       </c>
       <c r="E19" t="n">
-        <v>11.84740457834627</v>
+        <v>11.51090108984305</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586330384447832</v>
+        <v>0.758609140106669</v>
       </c>
       <c r="G19" t="n">
-        <v>20.76628250779837</v>
+        <v>20.00640839956468</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34138690842611</v>
+        <v>37.41942834411579</v>
       </c>
       <c r="I19" t="n">
-        <v>1.463488431850591</v>
+        <v>1.421274505104766</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741456490279897</v>
+        <v>4.741307125666679</v>
       </c>
       <c r="K19" t="n">
-        <v>21.871502982412</v>
+        <v>22.98383294880067</v>
       </c>
       <c r="L19" t="n">
-        <v>43.51915873844602</v>
+        <v>43.55521736653952</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95124749303385</v>
+        <v>99.9526533080637</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.57402876104599</v>
+        <v>74.42187910777305</v>
       </c>
       <c r="C20" t="n">
-        <v>32.23095921269085</v>
+        <v>31.03726836970591</v>
       </c>
       <c r="D20" t="n">
-        <v>1.119075414198714</v>
+        <v>1.066845598900007</v>
       </c>
       <c r="E20" t="n">
-        <v>11.16191471669812</v>
+        <v>10.80011714307311</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590413386963858</v>
+        <v>0.7590117860734321</v>
       </c>
       <c r="G20" t="n">
-        <v>19.20827461317714</v>
+        <v>18.42776745141135</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36148423730221</v>
+        <v>37.43928940444948</v>
       </c>
       <c r="I20" t="n">
-        <v>1.220230074121007</v>
+        <v>1.185024060906731</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744008366852412</v>
+        <v>4.743823662958948</v>
       </c>
       <c r="K20" t="n">
-        <v>24.42597123895403</v>
+        <v>25.57812089222695</v>
       </c>
       <c r="L20" t="n">
-        <v>43.30241709191483</v>
+        <v>43.34513089070311</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95934754355969</v>
+        <v>99.96052015263597</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.57408784779781</v>
+        <v>80.85307269884487</v>
       </c>
       <c r="C21" t="n">
-        <v>35.96030535361938</v>
+        <v>35.103793725343</v>
       </c>
       <c r="D21" t="n">
-        <v>1.119871312127481</v>
+        <v>1.067559590066864</v>
       </c>
       <c r="E21" t="n">
-        <v>13.17221364936082</v>
+        <v>12.96900449727021</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595811766926918</v>
+        <v>0.7595197580905221</v>
       </c>
       <c r="G21" t="n">
-        <v>20.93421455395946</v>
+        <v>20.33120325015464</v>
       </c>
       <c r="H21" t="n">
-        <v>39.10033492722349</v>
+        <v>39.35544874890263</v>
       </c>
       <c r="I21" t="n">
-        <v>1.74048987410455</v>
+        <v>1.623338366294253</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747382354329324</v>
+        <v>4.746998488065761</v>
       </c>
       <c r="K21" t="n">
-        <v>18.42591215220218</v>
+        <v>19.14692730115512</v>
       </c>
       <c r="L21" t="n">
-        <v>45.55580739752585</v>
+        <v>45.69520388461939</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94202490334742</v>
+        <v>99.9459249111175</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_23_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.56869704513804</v>
+        <v>43.27057548843829</v>
       </c>
       <c r="M2" t="n">
-        <v>99.65502237833525</v>
+        <v>95.64460538815558</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96133014537924</v>
+        <v>81.45279842264067</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87232959616418</v>
+        <v>43.20835397819623</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228604017765805</v>
+        <v>2.179150037837988</v>
       </c>
       <c r="E3" t="n">
-        <v>5.670653345358826</v>
+        <v>4.144150037202013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742868005921935</v>
+        <v>0.737615962759726</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95423214857374</v>
+        <v>32.77804848581307</v>
       </c>
       <c r="H3" t="n">
-        <v>34.171928272409</v>
+        <v>33.93033428694739</v>
       </c>
       <c r="I3" t="n">
-        <v>6.550119318337841</v>
+        <v>3.073399844832192</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642925037012093</v>
+        <v>4.610099767248287</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03866985462076</v>
+        <v>18.54720157735932</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85387149924038</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648709500253</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99713652273685</v>
+        <v>88.6110719065602</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54190268919149</v>
+        <v>42.83156130035067</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181825999491021</v>
+        <v>2.184907971200079</v>
       </c>
       <c r="E4" t="n">
-        <v>6.463272728566324</v>
+        <v>6.545662138516183</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444249128493743</v>
+        <v>0.7395649536445383</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24153860620792</v>
+        <v>33.47459938775024</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24354599107122</v>
+        <v>34.01998786764875</v>
       </c>
       <c r="I4" t="n">
-        <v>5.469872579242403</v>
+        <v>7.024068627522058</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652655705308589</v>
+        <v>4.622280960278364</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00286347726316</v>
+        <v>11.38892809343978</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27328607470263</v>
+        <v>45.54599200775748</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81805224115729</v>
+        <v>99.76648140154794</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.74376631786089</v>
+        <v>87.57501512787204</v>
       </c>
       <c r="C5" t="n">
-        <v>42.13739656713347</v>
+        <v>42.88424275957872</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120296648559983</v>
+        <v>2.136031606884063</v>
       </c>
       <c r="E5" t="n">
-        <v>7.042056071626702</v>
+        <v>7.376979210978566</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457464011387241</v>
+        <v>0.7412163488304651</v>
       </c>
       <c r="G5" t="n">
-        <v>32.30409891355317</v>
+        <v>32.72577301310448</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3043344523813</v>
+        <v>34.09595204620138</v>
       </c>
       <c r="I5" t="n">
-        <v>4.566318823483968</v>
+        <v>5.86646072168269</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660915007117025</v>
+        <v>4.632602180190406</v>
       </c>
       <c r="K5" t="n">
-        <v>14.25623368213911</v>
+        <v>12.42498487212794</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45442884574847</v>
+        <v>44.49565935086217</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84805909502106</v>
+        <v>99.80488698256883</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.24309656569893</v>
+        <v>86.36070131513166</v>
       </c>
       <c r="C6" t="n">
-        <v>41.34573923042274</v>
+        <v>42.580472578402</v>
       </c>
       <c r="D6" t="n">
-        <v>2.046644739578239</v>
+        <v>2.078545373647779</v>
       </c>
       <c r="E6" t="n">
-        <v>7.432606244637552</v>
+        <v>7.994771850448494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468709413011989</v>
+        <v>0.7426176218385844</v>
       </c>
       <c r="G6" t="n">
-        <v>31.18196416201538</v>
+        <v>31.84503631697789</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35606329985514</v>
+        <v>34.16041060457487</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811003795178937</v>
+        <v>4.897959411152883</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667943383132492</v>
+        <v>4.641360136491152</v>
       </c>
       <c r="K6" t="n">
-        <v>15.75690343430106</v>
+        <v>13.63929868486833</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77051514573497</v>
+        <v>43.6172714944607</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87315781045876</v>
+        <v>99.83704275773103</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.49109989011953</v>
+        <v>84.85860577231195</v>
       </c>
       <c r="C7" t="n">
-        <v>40.18539549461666</v>
+        <v>41.83914776053093</v>
       </c>
       <c r="D7" t="n">
-        <v>1.960976133666044</v>
+        <v>2.007281401901005</v>
       </c>
       <c r="E7" t="n">
-        <v>7.651477882713837</v>
+        <v>8.402031660769042</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478306358740625</v>
+        <v>0.7438101781795344</v>
       </c>
       <c r="G7" t="n">
-        <v>29.87674721463525</v>
+        <v>30.75321325786162</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40020925020687</v>
+        <v>34.21526819625857</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17991729881056</v>
+        <v>4.08818746372009</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67394147421289</v>
+        <v>4.64881361362209</v>
       </c>
       <c r="K7" t="n">
-        <v>17.5089001098805</v>
+        <v>15.14139422768805</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19984317897008</v>
+        <v>42.88340358369342</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89413878346724</v>
+        <v>99.8639455719124</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.41416705962507</v>
+        <v>83.27716795240192</v>
       </c>
       <c r="C8" t="n">
-        <v>42.5302743830599</v>
+        <v>40.89270249320673</v>
       </c>
       <c r="D8" t="n">
-        <v>1.965189388579419</v>
+        <v>1.932798597236054</v>
       </c>
       <c r="E8" t="n">
-        <v>9.513053393176014</v>
+        <v>8.658842431106654</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494373872500105</v>
+        <v>0.7448258586451534</v>
       </c>
       <c r="G8" t="n">
-        <v>30.39397262730248</v>
+        <v>29.6120750130019</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47411981350048</v>
+        <v>34.26198949767704</v>
       </c>
       <c r="I8" t="n">
-        <v>5.634410779504111</v>
+        <v>3.411474938202911</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683983670312564</v>
+        <v>4.655161616532208</v>
       </c>
       <c r="K8" t="n">
-        <v>12.58583294037493</v>
+        <v>16.72283204759808</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69648164585081</v>
+        <v>42.27090469631407</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81258896928564</v>
+        <v>99.88643923711888</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.18952941349377</v>
+        <v>81.4727153479834</v>
       </c>
       <c r="C9" t="n">
-        <v>41.17957220288552</v>
+        <v>39.61790525921053</v>
       </c>
       <c r="D9" t="n">
-        <v>1.864205377129014</v>
+        <v>1.848199008105561</v>
       </c>
       <c r="E9" t="n">
-        <v>9.808209233462184</v>
+        <v>8.754208156442129</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508167985110241</v>
+        <v>0.7456931952458191</v>
       </c>
       <c r="G9" t="n">
-        <v>28.83213573888048</v>
+        <v>28.31593925266776</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5375727315071</v>
+        <v>34.30188698130767</v>
       </c>
       <c r="I9" t="n">
-        <v>4.703984543310071</v>
+        <v>2.846206283928087</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692604990693899</v>
+        <v>4.660582470286369</v>
       </c>
       <c r="K9" t="n">
-        <v>14.81047058650623</v>
+        <v>18.5272846520166</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85344580006647</v>
+        <v>41.76004689604501</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84348858945822</v>
+        <v>99.90523680727215</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.82403631999493</v>
+        <v>86.13989207846141</v>
       </c>
       <c r="C10" t="n">
-        <v>39.54320524105472</v>
+        <v>42.83001299238322</v>
       </c>
       <c r="D10" t="n">
-        <v>1.758108180134441</v>
+        <v>1.850282507356286</v>
       </c>
       <c r="E10" t="n">
-        <v>9.904359858586904</v>
+        <v>10.59161470982818</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520031863178773</v>
+        <v>0.7465338250734251</v>
       </c>
       <c r="G10" t="n">
-        <v>27.19121740295479</v>
+        <v>29.6898647917386</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59214657062235</v>
+        <v>35.68256055863239</v>
       </c>
       <c r="I10" t="n">
-        <v>3.926181206891842</v>
+        <v>2.913199279123628</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700019914486732</v>
+        <v>4.665836406708906</v>
       </c>
       <c r="K10" t="n">
-        <v>17.17596368000505</v>
+        <v>13.86010792153858</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15016484162607</v>
+        <v>43.21288178977914</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86933376268584</v>
+        <v>99.90300270370093</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.31011954468347</v>
+        <v>85.95188739309815</v>
       </c>
       <c r="C11" t="n">
-        <v>37.63707479808416</v>
+        <v>43.00200701018522</v>
       </c>
       <c r="D11" t="n">
-        <v>1.646590869424793</v>
+        <v>1.835908048540648</v>
       </c>
       <c r="E11" t="n">
-        <v>9.822167916199225</v>
+        <v>10.9620354500226</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530257901532647</v>
+        <v>0.747252476447364</v>
       </c>
       <c r="G11" t="n">
-        <v>25.46647061321683</v>
+        <v>29.49820695104883</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63918634705017</v>
+        <v>35.75590692895192</v>
       </c>
       <c r="I11" t="n">
-        <v>3.276266820181272</v>
+        <v>2.482249560290769</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706411188457903</v>
+        <v>4.670327977796025</v>
       </c>
       <c r="K11" t="n">
-        <v>19.68988045531655</v>
+        <v>14.04811260690184</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56398415751895</v>
+        <v>42.86721830561697</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89093941091966</v>
+        <v>99.91733792270404</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.62767847368661</v>
+        <v>84.19447064520298</v>
       </c>
       <c r="C12" t="n">
-        <v>35.46085117635578</v>
+        <v>41.63074306153799</v>
       </c>
       <c r="D12" t="n">
-        <v>1.528798613248212</v>
+        <v>1.76106779447363</v>
       </c>
       <c r="E12" t="n">
-        <v>9.575090132776793</v>
+        <v>10.86021073918008</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539096419764759</v>
+        <v>0.7478649432401119</v>
       </c>
       <c r="G12" t="n">
-        <v>23.64467438800558</v>
+        <v>28.29572118140867</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67984353091789</v>
+        <v>35.78521336329482</v>
       </c>
       <c r="I12" t="n">
-        <v>2.733426904408707</v>
+        <v>2.070236728354971</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711935262352973</v>
+        <v>4.674155895250699</v>
       </c>
       <c r="K12" t="n">
-        <v>22.37232152631339</v>
+        <v>15.80552935479701</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07581988565913</v>
+        <v>42.49477620699026</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90899258832829</v>
+        <v>99.93104862332527</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.06346650514985</v>
+        <v>85.31684389060609</v>
       </c>
       <c r="C13" t="n">
-        <v>33.31790343308263</v>
+        <v>42.58020883164478</v>
       </c>
       <c r="D13" t="n">
-        <v>1.417417234325979</v>
+        <v>1.762386646223578</v>
       </c>
       <c r="E13" t="n">
-        <v>9.257519238716162</v>
+        <v>11.48609172880372</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546730121141394</v>
+        <v>0.7484250142335238</v>
       </c>
       <c r="G13" t="n">
-        <v>21.92202994374635</v>
+        <v>28.61519347253644</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71495855725041</v>
+        <v>36.1102944844184</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28016219328345</v>
+        <v>1.916796205430913</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716706325713369</v>
+        <v>4.677656338959523</v>
       </c>
       <c r="K13" t="n">
-        <v>24.93653349485014</v>
+        <v>14.68315610939389</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66963454694478</v>
+        <v>42.6727896654966</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92407147487755</v>
+        <v>99.93615460653527</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.38317558329875</v>
+        <v>83.46082040329638</v>
       </c>
       <c r="C14" t="n">
-        <v>37.90729432942032</v>
+        <v>41.02229506968627</v>
       </c>
       <c r="D14" t="n">
-        <v>1.419089246970081</v>
+        <v>1.68532649978159</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79190595381434</v>
+        <v>11.25025537578639</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555632389209392</v>
+        <v>0.7489027813271627</v>
       </c>
       <c r="G14" t="n">
-        <v>23.98545206353276</v>
+        <v>27.36399754218567</v>
       </c>
       <c r="H14" t="n">
-        <v>36.79347146179579</v>
+        <v>36.13334597270135</v>
       </c>
       <c r="I14" t="n">
-        <v>2.915423375008976</v>
+        <v>1.598349848219462</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722270243255868</v>
+        <v>4.680642383294766</v>
       </c>
       <c r="K14" t="n">
-        <v>17.61682441670125</v>
+        <v>16.53917959670361</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37881497596067</v>
+        <v>42.38528099457035</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90293372208224</v>
+        <v>99.94675566096024</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.44671590064884</v>
+        <v>82.63992224291339</v>
       </c>
       <c r="C15" t="n">
-        <v>37.42047073378391</v>
+        <v>40.42824778617487</v>
       </c>
       <c r="D15" t="n">
-        <v>1.384739054362572</v>
+        <v>1.650861394715736</v>
       </c>
       <c r="E15" t="n">
-        <v>11.91179635243578</v>
+        <v>11.24574276510917</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563152572311193</v>
+        <v>0.7493115903786333</v>
       </c>
       <c r="G15" t="n">
-        <v>23.40486497225598</v>
+        <v>26.804400899971</v>
       </c>
       <c r="H15" t="n">
-        <v>36.83009230676155</v>
+        <v>36.15307034716205</v>
       </c>
       <c r="I15" t="n">
-        <v>2.431937599907346</v>
+        <v>1.35333780571033</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726970357694492</v>
+        <v>4.683197439866457</v>
       </c>
       <c r="K15" t="n">
-        <v>18.55328409935116</v>
+        <v>17.36007775708662</v>
       </c>
       <c r="L15" t="n">
-        <v>43.94526118422581</v>
+        <v>42.16658780832746</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91901601736087</v>
+        <v>99.95491335158896</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.75211297680265</v>
+        <v>80.36310205460939</v>
       </c>
       <c r="C16" t="n">
-        <v>35.10088182353746</v>
+        <v>38.36146004599699</v>
       </c>
       <c r="D16" t="n">
-        <v>1.284173605487743</v>
+        <v>1.556914145460873</v>
       </c>
       <c r="E16" t="n">
-        <v>11.38477177889321</v>
+        <v>10.79382139022258</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756964583947542</v>
+        <v>0.7496622717333267</v>
       </c>
       <c r="G16" t="n">
-        <v>21.70510735772609</v>
+        <v>25.2790155826225</v>
       </c>
       <c r="H16" t="n">
-        <v>36.86171240522505</v>
+        <v>36.16999015442042</v>
       </c>
       <c r="I16" t="n">
-        <v>2.028354595850869</v>
+        <v>1.1283093118164</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731028649672134</v>
+        <v>4.685389198333291</v>
       </c>
       <c r="K16" t="n">
-        <v>21.24788702319738</v>
+        <v>19.63689794539062</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58367733104549</v>
+        <v>41.96404929178711</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93244617778034</v>
+        <v>99.96240728317471</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.57650455308153</v>
+        <v>84.8356991582318</v>
       </c>
       <c r="C17" t="n">
-        <v>36.42073124375717</v>
+        <v>41.30339436017962</v>
       </c>
       <c r="D17" t="n">
-        <v>1.285247153965925</v>
+        <v>1.557696876353687</v>
       </c>
       <c r="E17" t="n">
-        <v>12.20808696819384</v>
+        <v>12.36860024544451</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575973941639039</v>
+        <v>0.7500391607358277</v>
       </c>
       <c r="G17" t="n">
-        <v>22.20024687292376</v>
+        <v>26.64782315505082</v>
       </c>
       <c r="H17" t="n">
-        <v>37.36952259844758</v>
+        <v>37.54427311049468</v>
       </c>
       <c r="I17" t="n">
-        <v>2.020819851862116</v>
+        <v>1.279521855553357</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734983713524397</v>
+        <v>4.687744754598922</v>
       </c>
       <c r="K17" t="n">
-        <v>19.42349544691849</v>
+        <v>15.16430084176821</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08846891298835</v>
+        <v>43.48967550120205</v>
       </c>
       <c r="M17" t="n">
-        <v>99.932695603664</v>
+        <v>99.95737070314988</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.03259008436012</v>
+        <v>86.45119445800103</v>
       </c>
       <c r="C18" t="n">
-        <v>34.18793334439579</v>
+        <v>42.03562126233346</v>
       </c>
       <c r="D18" t="n">
-        <v>1.194505687936924</v>
+        <v>1.558967065653328</v>
       </c>
       <c r="E18" t="n">
-        <v>11.62703884413353</v>
+        <v>12.97087176801286</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581427752558604</v>
+        <v>0.7506507635006152</v>
       </c>
       <c r="G18" t="n">
-        <v>20.63285733135683</v>
+        <v>26.78940867832739</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3964242631017</v>
+        <v>37.57488775362049</v>
       </c>
       <c r="I18" t="n">
-        <v>1.685228837226155</v>
+        <v>2.114841157007507</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738392345349125</v>
+        <v>4.691567271878844</v>
       </c>
       <c r="K18" t="n">
-        <v>21.96740991563987</v>
+        <v>13.54880554199896</v>
       </c>
       <c r="L18" t="n">
-        <v>43.78852285519041</v>
+        <v>44.34513592693941</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94386611522607</v>
+        <v>99.92956273127183</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.01616705119932</v>
+        <v>83.99031621010489</v>
       </c>
       <c r="C19" t="n">
-        <v>33.41360299272351</v>
+        <v>39.90274796607127</v>
       </c>
       <c r="D19" t="n">
-        <v>1.15823844679769</v>
+        <v>1.467144783619596</v>
       </c>
       <c r="E19" t="n">
-        <v>11.51090108984305</v>
+        <v>12.50082825233687</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758609140106669</v>
+        <v>0.7511761607966302</v>
       </c>
       <c r="G19" t="n">
-        <v>20.00640839956468</v>
+        <v>25.21152759708247</v>
       </c>
       <c r="H19" t="n">
-        <v>37.41942834411579</v>
+        <v>37.60118725984061</v>
       </c>
       <c r="I19" t="n">
-        <v>1.421274505104766</v>
+        <v>1.763601151449772</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741307125666679</v>
+        <v>4.694851004978937</v>
       </c>
       <c r="K19" t="n">
-        <v>22.98383294880067</v>
+        <v>16.00968378989514</v>
       </c>
       <c r="L19" t="n">
-        <v>43.55521736653952</v>
+        <v>44.02882265633893</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9526533080637</v>
+        <v>99.94125441230533</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.42187910777305</v>
+        <v>81.33617110915067</v>
       </c>
       <c r="C20" t="n">
-        <v>31.03726836970591</v>
+        <v>37.52147629724937</v>
       </c>
       <c r="D20" t="n">
-        <v>1.066845598900007</v>
+        <v>1.368579986035737</v>
       </c>
       <c r="E20" t="n">
-        <v>10.80011714307311</v>
+        <v>11.90609769926893</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590117860734321</v>
+        <v>0.7516288682040314</v>
       </c>
       <c r="G20" t="n">
-        <v>18.42776745141135</v>
+        <v>23.51778261558471</v>
       </c>
       <c r="H20" t="n">
-        <v>37.43928940444948</v>
+        <v>37.6238481706735</v>
       </c>
       <c r="I20" t="n">
-        <v>1.185024060906731</v>
+        <v>1.470553343108553</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743823662958948</v>
+        <v>4.697680426275195</v>
       </c>
       <c r="K20" t="n">
-        <v>25.57812089222695</v>
+        <v>18.66382889084935</v>
       </c>
       <c r="L20" t="n">
-        <v>43.34513089070311</v>
+        <v>43.76570589102769</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96052015263597</v>
+        <v>99.9510110791264</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.85307269884487</v>
+        <v>78.67633187151181</v>
       </c>
       <c r="C21" t="n">
-        <v>35.103793725343</v>
+        <v>35.08849345133076</v>
       </c>
       <c r="D21" t="n">
-        <v>1.067559590066864</v>
+        <v>1.270300701597257</v>
       </c>
       <c r="E21" t="n">
-        <v>12.96900449727021</v>
+        <v>11.25545690810306</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595197580905221</v>
+        <v>0.7520193161786572</v>
       </c>
       <c r="G21" t="n">
-        <v>20.33120325015464</v>
+        <v>21.8289439137019</v>
       </c>
       <c r="H21" t="n">
-        <v>39.35544874890263</v>
+        <v>37.64339259736772</v>
       </c>
       <c r="I21" t="n">
-        <v>1.623338366294253</v>
+        <v>1.226097708446603</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746998488065761</v>
+        <v>4.700120726116607</v>
       </c>
       <c r="K21" t="n">
-        <v>19.14692730115512</v>
+        <v>21.32366812848819</v>
       </c>
       <c r="L21" t="n">
-        <v>45.69520388461939</v>
+        <v>43.54698971620583</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9459249111175</v>
+        <v>99.95915129602479</v>
       </c>
     </row>
   </sheetData>
